--- a/data/review/reviews_dataset.xlsx
+++ b/data/review/reviews_dataset.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECBA84FF-7ADD-0D4E-956C-B953B8732545}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25600" yWindow="0" windowWidth="32000" windowHeight="18000" xr2:uid="{53B64482-85E4-3145-A46A-B0D5C84CBA57}"/>
+    <workbookView xWindow="29520" yWindow="1640" windowWidth="25440" windowHeight="15300" activeTab="5" xr2:uid="{53B64482-85E4-3145-A46A-B0D5C84CBA57}"/>
   </bookViews>
   <sheets>
     <sheet name="type1_2np" sheetId="2" r:id="rId1"/>
